--- a/docs/BOM_JMS583硬盘盒.xlsx
+++ b/docs/BOM_JMS583硬盘盒.xlsx
@@ -296,7 +296,7 @@
     <t>C167223</t>
   </si>
   <si>
-    <t>磁珠2A）CBM160808U121T</t>
+    <t>(磁珠2A）CBM160808U121T</t>
   </si>
   <si>
     <t>L3</t>
@@ -314,7 +314,7 @@
     <t>C62708</t>
   </si>
   <si>
-    <t>磁珠4A）CBM201209U121T</t>
+    <t>(磁珠4A）CBM201209U121T</t>
   </si>
   <si>
     <t>L4</t>
